--- a/ملفات محدثةللاسترجاع/org_rev2/Hyperparameters_Obtimization/types of Transformers_best/comparison_output/trial_level_all_models.xlsx
+++ b/ملفات محدثةللاسترجاع/org_rev2/Hyperparameters_Obtimization/types of Transformers_best/comparison_output/trial_level_all_models.xlsx
@@ -523,7 +523,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>DAT+50T+50EP+optim_purn</t>
+          <t>DAT</t>
         </is>
       </c>
       <c r="B2" t="n">
@@ -579,7 +579,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>DAT+50T+50EP+optim_purn</t>
+          <t>DAT</t>
         </is>
       </c>
       <c r="B3" t="n">
@@ -635,7 +635,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>DAT+50T+50EP+optim_purn</t>
+          <t>DAT</t>
         </is>
       </c>
       <c r="B4" t="n">
@@ -691,7 +691,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>DAT+50T+50EP+optim_purn</t>
+          <t>DAT</t>
         </is>
       </c>
       <c r="B5" t="n">
@@ -747,7 +747,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>DAT+50T+50EP+optim_purn</t>
+          <t>DAT</t>
         </is>
       </c>
       <c r="B6" t="n">
@@ -803,7 +803,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>DAT+50T+50EP+optim_purn</t>
+          <t>DAT</t>
         </is>
       </c>
       <c r="B7" t="n">
@@ -859,7 +859,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>DAT+50T+50EP+optim_purn</t>
+          <t>DAT</t>
         </is>
       </c>
       <c r="B8" t="n">
@@ -915,7 +915,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>DAT+50T+50EP+optim_purn</t>
+          <t>DAT</t>
         </is>
       </c>
       <c r="B9" t="n">
@@ -971,7 +971,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>DAT+50T+50EP+optim_purn</t>
+          <t>DAT</t>
         </is>
       </c>
       <c r="B10" t="n">
@@ -1027,7 +1027,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>DAT+50T+50EP+optim_purn</t>
+          <t>DAT</t>
         </is>
       </c>
       <c r="B11" t="n">
@@ -1083,7 +1083,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>DAT+50T+50EP+optim_purn</t>
+          <t>DAT</t>
         </is>
       </c>
       <c r="B12" t="n">
@@ -1139,7 +1139,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>DAT+50T+50EP+optim_purn</t>
+          <t>DAT</t>
         </is>
       </c>
       <c r="B13" t="n">
@@ -1195,7 +1195,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>DAT+50T+50EP+optim_purn</t>
+          <t>DAT</t>
         </is>
       </c>
       <c r="B14" t="n">
@@ -1251,7 +1251,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>DAT+50T+50EP+optim_purn</t>
+          <t>DAT</t>
         </is>
       </c>
       <c r="B15" t="n">
@@ -1307,7 +1307,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>DAT+50T+50EP+optim_purn</t>
+          <t>DAT</t>
         </is>
       </c>
       <c r="B16" t="n">
@@ -1363,7 +1363,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>DAT+50T+50EP+optim_purn</t>
+          <t>DAT</t>
         </is>
       </c>
       <c r="B17" t="n">
@@ -1419,7 +1419,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>DAT+50T+50EP+optim_purn</t>
+          <t>DAT</t>
         </is>
       </c>
       <c r="B18" t="n">
@@ -1475,7 +1475,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>DAT+50T+50EP+optim_purn</t>
+          <t>DAT</t>
         </is>
       </c>
       <c r="B19" t="n">
@@ -1531,7 +1531,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>DAT+50T+50EP+optim_purn</t>
+          <t>DAT</t>
         </is>
       </c>
       <c r="B20" t="n">
@@ -1587,7 +1587,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>DAT+50T+50EP+optim_purn</t>
+          <t>DAT</t>
         </is>
       </c>
       <c r="B21" t="n">
@@ -1643,7 +1643,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>DAT+50T+50EP+optim_purn</t>
+          <t>DAT</t>
         </is>
       </c>
       <c r="B22" t="n">
@@ -1699,7 +1699,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>DAT+50T+50EP+optim_purn</t>
+          <t>DAT</t>
         </is>
       </c>
       <c r="B23" t="n">
@@ -1755,7 +1755,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>DAT+50T+50EP+optim_purn</t>
+          <t>DAT</t>
         </is>
       </c>
       <c r="B24" t="n">
@@ -1811,7 +1811,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>DAT+50T+50EP+optim_purn</t>
+          <t>DAT</t>
         </is>
       </c>
       <c r="B25" t="n">
@@ -1867,7 +1867,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>DAT+50T+50EP+optim_purn</t>
+          <t>DAT</t>
         </is>
       </c>
       <c r="B26" t="n">
@@ -1923,7 +1923,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>DAT+50T+50EP+optim_purn</t>
+          <t>DAT</t>
         </is>
       </c>
       <c r="B27" t="n">
@@ -1979,7 +1979,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>DAT+50T+50EP+optim_purn</t>
+          <t>DAT</t>
         </is>
       </c>
       <c r="B28" t="n">
@@ -2035,7 +2035,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>DAT+50T+50EP+optim_purn</t>
+          <t>DAT</t>
         </is>
       </c>
       <c r="B29" t="n">
@@ -2091,7 +2091,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>DAT+50T+50EP+optim_purn</t>
+          <t>DAT</t>
         </is>
       </c>
       <c r="B30" t="n">
@@ -2147,7 +2147,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>DAT+50T+50EP+optim_purn</t>
+          <t>DAT</t>
         </is>
       </c>
       <c r="B31" t="n">
@@ -2203,7 +2203,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>DAT+50T+50EP+optim_purn</t>
+          <t>DAT</t>
         </is>
       </c>
       <c r="B32" t="n">
@@ -2259,7 +2259,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>DAT+50T+50EP+optim_purn</t>
+          <t>DAT</t>
         </is>
       </c>
       <c r="B33" t="n">
@@ -2315,7 +2315,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>ELAN+50T+50EP+optim_purn</t>
+          <t>ELAN</t>
         </is>
       </c>
       <c r="B34" t="n">
@@ -2371,7 +2371,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>ELAN+50T+50EP+optim_purn</t>
+          <t>ELAN</t>
         </is>
       </c>
       <c r="B35" t="n">
@@ -2427,7 +2427,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>ELAN+50T+50EP+optim_purn</t>
+          <t>ELAN</t>
         </is>
       </c>
       <c r="B36" t="n">
@@ -2483,7 +2483,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>ELAN+50T+50EP+optim_purn</t>
+          <t>ELAN</t>
         </is>
       </c>
       <c r="B37" t="n">
@@ -2539,7 +2539,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>ELAN+50T+50EP+optim_purn</t>
+          <t>ELAN</t>
         </is>
       </c>
       <c r="B38" t="n">
@@ -2595,7 +2595,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>ELAN+50T+50EP+optim_purn</t>
+          <t>ELAN</t>
         </is>
       </c>
       <c r="B39" t="n">
@@ -2651,7 +2651,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>ELAN+50T+50EP+optim_purn</t>
+          <t>ELAN</t>
         </is>
       </c>
       <c r="B40" t="n">
@@ -2707,7 +2707,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>ELAN+50T+50EP+optim_purn</t>
+          <t>ELAN</t>
         </is>
       </c>
       <c r="B41" t="n">
@@ -2763,7 +2763,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>ELAN+50T+50EP+optim_purn</t>
+          <t>ELAN</t>
         </is>
       </c>
       <c r="B42" t="n">
@@ -2819,7 +2819,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>ELAN+50T+50EP+optim_purn</t>
+          <t>ELAN</t>
         </is>
       </c>
       <c r="B43" t="n">
@@ -2875,7 +2875,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>ELAN+50T+50EP+optim_purn</t>
+          <t>ELAN</t>
         </is>
       </c>
       <c r="B44" t="n">
@@ -2931,7 +2931,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>ELAN+50T+50EP+optim_purn</t>
+          <t>ELAN</t>
         </is>
       </c>
       <c r="B45" t="n">
@@ -2987,7 +2987,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>ELAN+50T+50EP+optim_purn</t>
+          <t>ELAN</t>
         </is>
       </c>
       <c r="B46" t="n">
@@ -3043,7 +3043,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>ELAN+50T+50EP+optim_purn</t>
+          <t>ELAN</t>
         </is>
       </c>
       <c r="B47" t="n">
@@ -3099,7 +3099,7 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>ELAN+50T+50EP+optim_purn</t>
+          <t>ELAN</t>
         </is>
       </c>
       <c r="B48" t="n">
@@ -3155,7 +3155,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>ELAN+50T+50EP+optim_purn</t>
+          <t>ELAN</t>
         </is>
       </c>
       <c r="B49" t="n">
@@ -3211,7 +3211,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>ELAN+50T+50EP+optim_purn</t>
+          <t>ELAN</t>
         </is>
       </c>
       <c r="B50" t="n">
@@ -3267,7 +3267,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>ELAN+50T+50EP+optim_purn</t>
+          <t>ELAN</t>
         </is>
       </c>
       <c r="B51" t="n">
@@ -3323,7 +3323,7 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>ELAN+50T+50EP+optim_purn</t>
+          <t>ELAN</t>
         </is>
       </c>
       <c r="B52" t="n">
@@ -3379,7 +3379,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>ELAN+50T+50EP+optim_purn</t>
+          <t>ELAN</t>
         </is>
       </c>
       <c r="B53" t="n">
@@ -3435,7 +3435,7 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>ELAN+50T+50EP+optim_purn</t>
+          <t>ELAN</t>
         </is>
       </c>
       <c r="B54" t="n">
@@ -3491,7 +3491,7 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>HAT+50T+50EP+optim_purn</t>
+          <t>HAT</t>
         </is>
       </c>
       <c r="B55" t="n">
@@ -3547,7 +3547,7 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>HAT+50T+50EP+optim_purn</t>
+          <t>HAT</t>
         </is>
       </c>
       <c r="B56" t="n">
@@ -3603,7 +3603,7 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>HAT+50T+50EP+optim_purn</t>
+          <t>HAT</t>
         </is>
       </c>
       <c r="B57" t="n">
@@ -3659,7 +3659,7 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>HAT+50T+50EP+optim_purn</t>
+          <t>HAT</t>
         </is>
       </c>
       <c r="B58" t="n">
@@ -3715,7 +3715,7 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>HAT+50T+50EP+optim_purn</t>
+          <t>HAT</t>
         </is>
       </c>
       <c r="B59" t="n">
@@ -3771,7 +3771,7 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>HAT+50T+50EP+optim_purn</t>
+          <t>HAT</t>
         </is>
       </c>
       <c r="B60" t="n">
@@ -3827,7 +3827,7 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>HAT+50T+50EP+optim_purn</t>
+          <t>HAT</t>
         </is>
       </c>
       <c r="B61" t="n">
@@ -3883,7 +3883,7 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>HAT+50T+50EP+optim_purn</t>
+          <t>HAT</t>
         </is>
       </c>
       <c r="B62" t="n">
@@ -3939,7 +3939,7 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>HAT+50T+50EP+optim_purn</t>
+          <t>HAT</t>
         </is>
       </c>
       <c r="B63" t="n">
@@ -3995,7 +3995,7 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>HAT+50T+50EP+optim_purn</t>
+          <t>HAT</t>
         </is>
       </c>
       <c r="B64" t="n">
@@ -4051,7 +4051,7 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>HAT+50T+50EP+optim_purn</t>
+          <t>HAT</t>
         </is>
       </c>
       <c r="B65" t="n">
@@ -4107,7 +4107,7 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>HAT+50T+50EP+optim_purn</t>
+          <t>HAT</t>
         </is>
       </c>
       <c r="B66" t="n">
@@ -4163,7 +4163,7 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>HAT+50T+50EP+optim_purn</t>
+          <t>HAT</t>
         </is>
       </c>
       <c r="B67" t="n">
@@ -4219,7 +4219,7 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>HAT+50T+50EP+optim_purn</t>
+          <t>HAT</t>
         </is>
       </c>
       <c r="B68" t="n">
@@ -4275,7 +4275,7 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>HAT+50T+50EP+optim_purn</t>
+          <t>HAT</t>
         </is>
       </c>
       <c r="B69" t="n">
@@ -4331,7 +4331,7 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>HAT+50T+50EP+optim_purn</t>
+          <t>HAT</t>
         </is>
       </c>
       <c r="B70" t="n">
@@ -4387,7 +4387,7 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>HAT+50T+50EP+optim_purn</t>
+          <t>HAT</t>
         </is>
       </c>
       <c r="B71" t="n">
@@ -4443,7 +4443,7 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>HAT+50T+50EP+optim_purn</t>
+          <t>HAT</t>
         </is>
       </c>
       <c r="B72" t="n">
@@ -4499,7 +4499,7 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>HAT+50T+50EP+optim_purn</t>
+          <t>HAT</t>
         </is>
       </c>
       <c r="B73" t="n">
@@ -4555,7 +4555,7 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>HAT+50T+50EP+optim_purn</t>
+          <t>HAT</t>
         </is>
       </c>
       <c r="B74" t="n">
@@ -4611,7 +4611,7 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>HAT+50T+50EP+optim_purn</t>
+          <t>HAT</t>
         </is>
       </c>
       <c r="B75" t="n">
@@ -4667,7 +4667,7 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>HAT+50T+50EP+optim_purn</t>
+          <t>HAT</t>
         </is>
       </c>
       <c r="B76" t="n">
@@ -4723,7 +4723,7 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>HAT+50T+50EP+optim_purn</t>
+          <t>HAT</t>
         </is>
       </c>
       <c r="B77" t="n">
@@ -4779,7 +4779,7 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>HAT+50T+50EP+optim_purn</t>
+          <t>HAT</t>
         </is>
       </c>
       <c r="B78" t="n">
@@ -4835,7 +4835,7 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>HAT+50T+50EP+optim_purn</t>
+          <t>HAT</t>
         </is>
       </c>
       <c r="B79" t="n">
@@ -4891,7 +4891,7 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>HAT+50T+50EP+optim_purn</t>
+          <t>HAT</t>
         </is>
       </c>
       <c r="B80" t="n">
@@ -4947,7 +4947,7 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>HAT+50T+50EP+optim_purn</t>
+          <t>HAT</t>
         </is>
       </c>
       <c r="B81" t="n">
@@ -5003,7 +5003,7 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>HAT+50T+50EP+optim_purn</t>
+          <t>HAT</t>
         </is>
       </c>
       <c r="B82" t="n">
@@ -5059,7 +5059,7 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>OmniSR+50T+50EP+optim_purn</t>
+          <t>Omni-SR</t>
         </is>
       </c>
       <c r="B83" t="n">
@@ -5115,7 +5115,7 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>OmniSR+50T+50EP+optim_purn</t>
+          <t>Omni-SR</t>
         </is>
       </c>
       <c r="B84" t="n">
@@ -5171,7 +5171,7 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>OmniSR+50T+50EP+optim_purn</t>
+          <t>Omni-SR</t>
         </is>
       </c>
       <c r="B85" t="n">
@@ -5227,7 +5227,7 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>OmniSR+50T+50EP+optim_purn</t>
+          <t>Omni-SR</t>
         </is>
       </c>
       <c r="B86" t="n">
@@ -5283,7 +5283,7 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>OmniSR+50T+50EP+optim_purn</t>
+          <t>Omni-SR</t>
         </is>
       </c>
       <c r="B87" t="n">
@@ -5339,7 +5339,7 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>OmniSR+50T+50EP+optim_purn</t>
+          <t>Omni-SR</t>
         </is>
       </c>
       <c r="B88" t="n">
@@ -5395,7 +5395,7 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>OmniSR+50T+50EP+optim_purn</t>
+          <t>Omni-SR</t>
         </is>
       </c>
       <c r="B89" t="n">
@@ -5451,7 +5451,7 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>OmniSR+50T+50EP+optim_purn</t>
+          <t>Omni-SR</t>
         </is>
       </c>
       <c r="B90" t="n">
@@ -5507,7 +5507,7 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>OmniSR+50T+50EP+optim_purn</t>
+          <t>Omni-SR</t>
         </is>
       </c>
       <c r="B91" t="n">
@@ -5563,7 +5563,7 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>OmniSR+50T+50EP+optim_purn</t>
+          <t>Omni-SR</t>
         </is>
       </c>
       <c r="B92" t="n">
@@ -5619,7 +5619,7 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>OmniSR+50T+50EP+optim_purn</t>
+          <t>Omni-SR</t>
         </is>
       </c>
       <c r="B93" t="n">
@@ -5675,7 +5675,7 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>OmniSR+50T+50EP+optim_purn</t>
+          <t>Omni-SR</t>
         </is>
       </c>
       <c r="B94" t="n">
@@ -5731,7 +5731,7 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>OmniSR+50T+50EP+optim_purn</t>
+          <t>Omni-SR</t>
         </is>
       </c>
       <c r="B95" t="n">
@@ -5787,7 +5787,7 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>OmniSR+50T+50EP+optim_purn</t>
+          <t>Omni-SR</t>
         </is>
       </c>
       <c r="B96" t="n">
@@ -5843,7 +5843,7 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>OmniSR+50T+50EP+optim_purn</t>
+          <t>Omni-SR</t>
         </is>
       </c>
       <c r="B97" t="n">
@@ -5899,7 +5899,7 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>OmniSR+50T+50EP+optim_purn</t>
+          <t>Omni-SR</t>
         </is>
       </c>
       <c r="B98" t="n">
@@ -5955,7 +5955,7 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>OmniSR+50T+50EP+optim_purn</t>
+          <t>Omni-SR</t>
         </is>
       </c>
       <c r="B99" t="n">
@@ -6011,7 +6011,7 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>OmniSR+50T+50EP+optim_purn</t>
+          <t>Omni-SR</t>
         </is>
       </c>
       <c r="B100" t="n">
@@ -6067,7 +6067,7 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>OmniSR+50T+50EP+optim_purn</t>
+          <t>Omni-SR</t>
         </is>
       </c>
       <c r="B101" t="n">
@@ -6123,7 +6123,7 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>OmniSR+50T+50EP+optim_purn</t>
+          <t>Omni-SR</t>
         </is>
       </c>
       <c r="B102" t="n">
@@ -6179,7 +6179,7 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>OmniSR+50T+50EP+optim_purn</t>
+          <t>Omni-SR</t>
         </is>
       </c>
       <c r="B103" t="n">
@@ -6235,7 +6235,7 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>OmniSR+50T+50EP+optim_purn</t>
+          <t>Omni-SR</t>
         </is>
       </c>
       <c r="B104" t="n">
@@ -6291,7 +6291,7 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>OmniSR+50T+50EP+optim_purn</t>
+          <t>Omni-SR</t>
         </is>
       </c>
       <c r="B105" t="n">
@@ -6347,7 +6347,7 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>OmniSR+50T+50EP+optim_purn</t>
+          <t>Omni-SR</t>
         </is>
       </c>
       <c r="B106" t="n">
@@ -6403,7 +6403,7 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>OmniSR+50T+50EP+optim_purn</t>
+          <t>Omni-SR</t>
         </is>
       </c>
       <c r="B107" t="n">
@@ -6459,7 +6459,7 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>OmniSR+50T+50EP+optim_purn</t>
+          <t>Omni-SR</t>
         </is>
       </c>
       <c r="B108" t="n">
@@ -6515,7 +6515,7 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>DHTCUN+50T+50EP+optim_purn</t>
+          <t>Org_rev2_best</t>
         </is>
       </c>
       <c r="B109" t="n">
@@ -6573,7 +6573,7 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>DHTCUN+50T+50EP+optim_purn</t>
+          <t>Org_rev2_best</t>
         </is>
       </c>
       <c r="B110" t="n">
@@ -6631,7 +6631,7 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>DHTCUN+50T+50EP+optim_purn</t>
+          <t>Org_rev2_best</t>
         </is>
       </c>
       <c r="B111" t="n">
@@ -6689,7 +6689,7 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>DHTCUN+50T+50EP+optim_purn</t>
+          <t>Org_rev2_best</t>
         </is>
       </c>
       <c r="B112" t="n">
@@ -6747,7 +6747,7 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>DHTCUN+50T+50EP+optim_purn</t>
+          <t>Org_rev2_best</t>
         </is>
       </c>
       <c r="B113" t="n">
@@ -6805,7 +6805,7 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>DHTCUN+50T+50EP+optim_purn</t>
+          <t>Org_rev2_best</t>
         </is>
       </c>
       <c r="B114" t="n">
@@ -6863,7 +6863,7 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>DHTCUN+50T+50EP+optim_purn</t>
+          <t>Org_rev2_best</t>
         </is>
       </c>
       <c r="B115" t="n">
@@ -6921,7 +6921,7 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>DHTCUN+50T+50EP+optim_purn</t>
+          <t>Org_rev2_best</t>
         </is>
       </c>
       <c r="B116" t="n">
@@ -6979,7 +6979,7 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>DHTCUN+50T+50EP+optim_purn</t>
+          <t>Org_rev2_best</t>
         </is>
       </c>
       <c r="B117" t="n">
@@ -7037,7 +7037,7 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>DHTCUN+50T+50EP+optim_purn</t>
+          <t>Org_rev2_best</t>
         </is>
       </c>
       <c r="B118" t="n">
@@ -7095,7 +7095,7 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>DHTCUN+50T+50EP+optim_purn</t>
+          <t>Org_rev2_best</t>
         </is>
       </c>
       <c r="B119" t="n">
@@ -7153,7 +7153,7 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>DHTCUN+50T+50EP+optim_purn</t>
+          <t>Org_rev2_best</t>
         </is>
       </c>
       <c r="B120" t="n">
@@ -7211,7 +7211,7 @@
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>DHTCUN+50T+50EP+optim_purn</t>
+          <t>Org_rev2_best</t>
         </is>
       </c>
       <c r="B121" t="n">
@@ -7269,7 +7269,7 @@
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>DHTCUN+50T+50EP+optim_purn</t>
+          <t>Org_rev2_best</t>
         </is>
       </c>
       <c r="B122" t="n">
@@ -7327,7 +7327,7 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>DHTCUN+50T+50EP+optim_purn</t>
+          <t>Org_rev2_best</t>
         </is>
       </c>
       <c r="B123" t="n">
@@ -7385,7 +7385,7 @@
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>DHTCUN+50T+50EP+optim_purn</t>
+          <t>Org_rev2_best</t>
         </is>
       </c>
       <c r="B124" t="n">
@@ -7443,7 +7443,7 @@
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>DHTCUN+50T+50EP+optim_purn</t>
+          <t>Org_rev2_best</t>
         </is>
       </c>
       <c r="B125" t="n">
@@ -7501,7 +7501,7 @@
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>DHTCUN+50T+50EP+optim_purn</t>
+          <t>Org_rev2_best</t>
         </is>
       </c>
       <c r="B126" t="n">
@@ -7559,7 +7559,7 @@
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>DHTCUN+50T+50EP+optim_purn</t>
+          <t>Org_rev2_best</t>
         </is>
       </c>
       <c r="B127" t="n">
@@ -7617,7 +7617,7 @@
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>DHTCUN+50T+50EP+optim_purn</t>
+          <t>Org_rev2_best</t>
         </is>
       </c>
       <c r="B128" t="n">
@@ -7675,7 +7675,7 @@
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>DHTCUN+50T+50EP+optim_purn</t>
+          <t>Org_rev2_best</t>
         </is>
       </c>
       <c r="B129" t="n">
@@ -7733,7 +7733,7 @@
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>DHTCUN+50T+50EP+optim_purn</t>
+          <t>Org_rev2_best</t>
         </is>
       </c>
       <c r="B130" t="n">
@@ -7791,7 +7791,7 @@
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>DHTCUN+50T+50EP+optim_purn</t>
+          <t>Org_rev2_best</t>
         </is>
       </c>
       <c r="B131" t="n">
@@ -7849,7 +7849,7 @@
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>DHTCUN+50T+50EP+optim_purn</t>
+          <t>Org_rev2_best</t>
         </is>
       </c>
       <c r="B132" t="n">
@@ -7907,7 +7907,7 @@
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>DHTCUN+50T+50EP+optim_purn</t>
+          <t>Org_rev2_best</t>
         </is>
       </c>
       <c r="B133" t="n">
@@ -7965,7 +7965,7 @@
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>DHTCUN+50T+50EP+optim_purn</t>
+          <t>Org_rev2_best</t>
         </is>
       </c>
       <c r="B134" t="n">
@@ -8023,7 +8023,7 @@
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>DHTCUN+50T+50EP+optim_purn</t>
+          <t>Org_rev2_best</t>
         </is>
       </c>
       <c r="B135" t="n">
@@ -8081,7 +8081,7 @@
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>DHTCUN+50T+50EP+optim_purn</t>
+          <t>Org_rev2_best</t>
         </is>
       </c>
       <c r="B136" t="n">
@@ -8139,7 +8139,7 @@
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>DHTCUN+50T+50EP+optim_purn</t>
+          <t>Org_rev2_best</t>
         </is>
       </c>
       <c r="B137" t="n">
@@ -8197,7 +8197,7 @@
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>DHTCUN+50T+50EP+optim_purn</t>
+          <t>Org_rev2_best</t>
         </is>
       </c>
       <c r="B138" t="n">
@@ -8255,7 +8255,7 @@
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>DHTCUN+50T+50EP+optim_purn</t>
+          <t>Org_rev2_best</t>
         </is>
       </c>
       <c r="B139" t="n">
@@ -8313,7 +8313,7 @@
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>DHTCUN+50T+50EP+optim_purn</t>
+          <t>Org_rev2_best</t>
         </is>
       </c>
       <c r="B140" t="n">
@@ -8371,7 +8371,7 @@
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>DHTCUN+50T+50EP+optim_purn</t>
+          <t>Org_rev2_best</t>
         </is>
       </c>
       <c r="B141" t="n">
@@ -8429,7 +8429,7 @@
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>DHTCUN+50T+50EP+optim_purn</t>
+          <t>Org_rev2_best</t>
         </is>
       </c>
       <c r="B142" t="n">
@@ -8487,7 +8487,7 @@
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>DHTCUN+50T+50EP+optim_purn</t>
+          <t>Org_rev2_best</t>
         </is>
       </c>
       <c r="B143" t="n">
@@ -8545,7 +8545,7 @@
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>SRFormer2+50T+50EP+optim_purn</t>
+          <t>SRFormer2</t>
         </is>
       </c>
       <c r="B144" t="n">
@@ -8603,7 +8603,7 @@
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>SRFormer2+50T+50EP+optim_purn</t>
+          <t>SRFormer2</t>
         </is>
       </c>
       <c r="B145" t="n">
@@ -8661,7 +8661,7 @@
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>SRFormer2+50T+50EP+optim_purn</t>
+          <t>SRFormer2</t>
         </is>
       </c>
       <c r="B146" t="n">
@@ -8719,7 +8719,7 @@
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>SRFormer2+50T+50EP+optim_purn</t>
+          <t>SRFormer2</t>
         </is>
       </c>
       <c r="B147" t="n">
@@ -8777,7 +8777,7 @@
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>SRFormer2+50T+50EP+optim_purn</t>
+          <t>SRFormer2</t>
         </is>
       </c>
       <c r="B148" t="n">
@@ -8835,7 +8835,7 @@
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>SRFormer2+50T+50EP+optim_purn</t>
+          <t>SRFormer2</t>
         </is>
       </c>
       <c r="B149" t="n">
@@ -8893,7 +8893,7 @@
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>SRFormer2+50T+50EP+optim_purn</t>
+          <t>SRFormer2</t>
         </is>
       </c>
       <c r="B150" t="n">
@@ -8951,7 +8951,7 @@
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>SRFormer2+50T+50EP+optim_purn</t>
+          <t>SRFormer2</t>
         </is>
       </c>
       <c r="B151" t="n">
@@ -9009,7 +9009,7 @@
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>SRFormer2+50T+50EP+optim_purn</t>
+          <t>SRFormer2</t>
         </is>
       </c>
       <c r="B152" t="n">
@@ -9067,7 +9067,7 @@
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>SRFormer2+50T+50EP+optim_purn</t>
+          <t>SRFormer2</t>
         </is>
       </c>
       <c r="B153" t="n">
@@ -9125,7 +9125,7 @@
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>SRFormer2+50T+50EP+optim_purn</t>
+          <t>SRFormer2</t>
         </is>
       </c>
       <c r="B154" t="n">
@@ -9183,7 +9183,7 @@
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>SRFormer2+50T+50EP+optim_purn</t>
+          <t>SRFormer2</t>
         </is>
       </c>
       <c r="B155" t="n">
@@ -9241,7 +9241,7 @@
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>SRFormer2+50T+50EP+optim_purn</t>
+          <t>SRFormer2</t>
         </is>
       </c>
       <c r="B156" t="n">
@@ -9299,7 +9299,7 @@
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>SRFormer2+50T+50EP+optim_purn</t>
+          <t>SRFormer2</t>
         </is>
       </c>
       <c r="B157" t="n">
@@ -9357,7 +9357,7 @@
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>SRFormer2+50T+50EP+optim_purn</t>
+          <t>SRFormer2</t>
         </is>
       </c>
       <c r="B158" t="n">
@@ -9415,7 +9415,7 @@
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>SRFormer2+50T+50EP+optim_purn</t>
+          <t>SRFormer2</t>
         </is>
       </c>
       <c r="B159" t="n">
@@ -9473,7 +9473,7 @@
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>SRFormer2+50T+50EP+optim_purn</t>
+          <t>SRFormer2</t>
         </is>
       </c>
       <c r="B160" t="n">
@@ -9531,7 +9531,7 @@
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>SRFormer2+50T+50EP+optim_purn</t>
+          <t>SRFormer2</t>
         </is>
       </c>
       <c r="B161" t="n">
@@ -9589,7 +9589,7 @@
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>SRFormer2+50T+50EP+optim_purn</t>
+          <t>SRFormer2</t>
         </is>
       </c>
       <c r="B162" t="n">
@@ -9647,7 +9647,7 @@
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>SRFormer2+50T+50EP+optim_purn</t>
+          <t>SRFormer2</t>
         </is>
       </c>
       <c r="B163" t="n">
@@ -9705,7 +9705,7 @@
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>SRFormer2+50T+50EP+optim_purn</t>
+          <t>SRFormer2</t>
         </is>
       </c>
       <c r="B164" t="n">
@@ -9763,7 +9763,7 @@
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>SRFormer2+50T+50EP+optim_purn</t>
+          <t>SRFormer2</t>
         </is>
       </c>
       <c r="B165" t="n">
@@ -9821,7 +9821,7 @@
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>SRFormer2+50T+50EP+optim_purn</t>
+          <t>SRFormer2</t>
         </is>
       </c>
       <c r="B166" t="n">
@@ -9879,7 +9879,7 @@
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>SRFormer2+50T+50EP+optim_purn</t>
+          <t>SRFormer2</t>
         </is>
       </c>
       <c r="B167" t="n">
@@ -9937,7 +9937,7 @@
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>SRFormer2+50T+50EP+optim_purn</t>
+          <t>SRFormer2</t>
         </is>
       </c>
       <c r="B168" t="n">
@@ -9995,7 +9995,7 @@
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>SRFormer2+50T+50EP+optim_purn</t>
+          <t>SRFormer2</t>
         </is>
       </c>
       <c r="B169" t="n">
@@ -10053,7 +10053,7 @@
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>SRFormer2+50T+50EP+optim_purn</t>
+          <t>SRFormer2</t>
         </is>
       </c>
       <c r="B170" t="n">
@@ -10111,7 +10111,7 @@
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>SRFormer2+50T+50EP+optim_purn</t>
+          <t>SRFormer2</t>
         </is>
       </c>
       <c r="B171" t="n">
@@ -10169,7 +10169,7 @@
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>SRFormer2+50T+50EP+optim_purn</t>
+          <t>SRFormer2</t>
         </is>
       </c>
       <c r="B172" t="n">
@@ -10227,7 +10227,7 @@
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>SRFormer2+50T+50EP+optim_purn</t>
+          <t>SRFormer2</t>
         </is>
       </c>
       <c r="B173" t="n">
@@ -10285,7 +10285,7 @@
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>SRFormer2+50T+50EP+optim_purn</t>
+          <t>SRFormer2</t>
         </is>
       </c>
       <c r="B174" t="n">
@@ -10343,7 +10343,7 @@
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>SRFormer2+50T+50EP+optim_purn</t>
+          <t>SRFormer2</t>
         </is>
       </c>
       <c r="B175" t="n">
@@ -10401,7 +10401,7 @@
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>SwinT2+50T+50EP+optim_purn</t>
+          <t>Swint_2</t>
         </is>
       </c>
       <c r="B176" t="n">
@@ -10457,7 +10457,7 @@
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>SwinT2+50T+50EP+optim_purn</t>
+          <t>Swint_2</t>
         </is>
       </c>
       <c r="B177" t="n">
@@ -10513,7 +10513,7 @@
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>SwinT2+50T+50EP+optim_purn</t>
+          <t>Swint_2</t>
         </is>
       </c>
       <c r="B178" t="n">
@@ -10569,7 +10569,7 @@
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>SwinT2+50T+50EP+optim_purn</t>
+          <t>Swint_2</t>
         </is>
       </c>
       <c r="B179" t="n">
@@ -10625,7 +10625,7 @@
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>SwinT2+50T+50EP+optim_purn</t>
+          <t>Swint_2</t>
         </is>
       </c>
       <c r="B180" t="n">
@@ -10681,7 +10681,7 @@
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>SwinT2+50T+50EP+optim_purn</t>
+          <t>Swint_2</t>
         </is>
       </c>
       <c r="B181" t="n">
@@ -10737,7 +10737,7 @@
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>SwinT2+50T+50EP+optim_purn</t>
+          <t>Swint_2</t>
         </is>
       </c>
       <c r="B182" t="n">
@@ -10793,7 +10793,7 @@
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>SwinT2+50T+50EP+optim_purn</t>
+          <t>Swint_2</t>
         </is>
       </c>
       <c r="B183" t="n">
@@ -10849,7 +10849,7 @@
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>SwinT2+50T+50EP+optim_purn</t>
+          <t>Swint_2</t>
         </is>
       </c>
       <c r="B184" t="n">
@@ -10905,7 +10905,7 @@
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>SwinT2+50T+50EP+optim_purn</t>
+          <t>Swint_2</t>
         </is>
       </c>
       <c r="B185" t="n">
@@ -10961,7 +10961,7 @@
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>SwinT2+50T+50EP+optim_purn</t>
+          <t>Swint_2</t>
         </is>
       </c>
       <c r="B186" t="n">
@@ -11017,7 +11017,7 @@
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>SwinT2+50T+50EP+optim_purn</t>
+          <t>Swint_2</t>
         </is>
       </c>
       <c r="B187" t="n">
@@ -11073,7 +11073,7 @@
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>SwinT2+50T+50EP+optim_purn</t>
+          <t>Swint_2</t>
         </is>
       </c>
       <c r="B188" t="n">
@@ -11129,7 +11129,7 @@
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>SwinT2+50T+50EP+optim_purn</t>
+          <t>Swint_2</t>
         </is>
       </c>
       <c r="B189" t="n">
@@ -11185,7 +11185,7 @@
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>SwinT2+50T+50EP+optim_purn</t>
+          <t>Swint_2</t>
         </is>
       </c>
       <c r="B190" t="n">
@@ -11241,7 +11241,7 @@
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>SwinT2+50T+50EP+optim_purn</t>
+          <t>Swint_2</t>
         </is>
       </c>
       <c r="B191" t="n">
@@ -11297,7 +11297,7 @@
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>SwinT2+50T+50EP+optim_purn</t>
+          <t>Swint_2</t>
         </is>
       </c>
       <c r="B192" t="n">
@@ -11353,7 +11353,7 @@
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>SwinT2+50T+50EP+optim_purn</t>
+          <t>Swint_2</t>
         </is>
       </c>
       <c r="B193" t="n">
@@ -11409,7 +11409,7 @@
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>SwinT2+50T+50EP+optim_purn</t>
+          <t>Swint_2</t>
         </is>
       </c>
       <c r="B194" t="n">
@@ -11465,7 +11465,7 @@
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>SwinT2+50T+50EP+optim_purn</t>
+          <t>Swint_2</t>
         </is>
       </c>
       <c r="B195" t="n">
@@ -11521,7 +11521,7 @@
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>SwinT2+50T+50EP+optim_purn</t>
+          <t>Swint_2</t>
         </is>
       </c>
       <c r="B196" t="n">
@@ -11577,7 +11577,7 @@
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>SwinT2+50T+50EP+optim_purn</t>
+          <t>Swint_2</t>
         </is>
       </c>
       <c r="B197" t="n">
@@ -11633,7 +11633,7 @@
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>SwinT2+50T+50EP+optim_purn</t>
+          <t>Swint_2</t>
         </is>
       </c>
       <c r="B198" t="n">
@@ -11689,7 +11689,7 @@
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>SwinT2+50T+50EP+optim_purn</t>
+          <t>Swint_2</t>
         </is>
       </c>
       <c r="B199" t="n">
@@ -11745,7 +11745,7 @@
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>SwinT2+50T+50EP+optim_purn</t>
+          <t>Swint_2</t>
         </is>
       </c>
       <c r="B200" t="n">
@@ -11801,7 +11801,7 @@
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>SwinT2+50T+50EP+optim_purn</t>
+          <t>Swint_2</t>
         </is>
       </c>
       <c r="B201" t="n">
@@ -11857,7 +11857,7 @@
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>Wavelet+50T+50EP+optim_purn</t>
+          <t>Wavelet Trans</t>
         </is>
       </c>
       <c r="B202" t="n">
@@ -11913,7 +11913,7 @@
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>Wavelet+50T+50EP+optim_purn</t>
+          <t>Wavelet Trans</t>
         </is>
       </c>
       <c r="B203" t="n">
@@ -11969,7 +11969,7 @@
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>Wavelet+50T+50EP+optim_purn</t>
+          <t>Wavelet Trans</t>
         </is>
       </c>
       <c r="B204" t="n">
@@ -12025,7 +12025,7 @@
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>Wavelet+50T+50EP+optim_purn</t>
+          <t>Wavelet Trans</t>
         </is>
       </c>
       <c r="B205" t="n">
@@ -12081,7 +12081,7 @@
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>Wavelet+50T+50EP+optim_purn</t>
+          <t>Wavelet Trans</t>
         </is>
       </c>
       <c r="B206" t="n">
@@ -12137,7 +12137,7 @@
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>Wavelet+50T+50EP+optim_purn</t>
+          <t>Wavelet Trans</t>
         </is>
       </c>
       <c r="B207" t="n">
@@ -12193,7 +12193,7 @@
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>Wavelet+50T+50EP+optim_purn</t>
+          <t>Wavelet Trans</t>
         </is>
       </c>
       <c r="B208" t="n">
@@ -12249,7 +12249,7 @@
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>Wavelet+50T+50EP+optim_purn</t>
+          <t>Wavelet Trans</t>
         </is>
       </c>
       <c r="B209" t="n">
@@ -12305,7 +12305,7 @@
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>Wavelet+50T+50EP+optim_purn</t>
+          <t>Wavelet Trans</t>
         </is>
       </c>
       <c r="B210" t="n">
@@ -12361,7 +12361,7 @@
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>Wavelet+50T+50EP+optim_purn</t>
+          <t>Wavelet Trans</t>
         </is>
       </c>
       <c r="B211" t="n">
@@ -12417,7 +12417,7 @@
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>Wavelet+50T+50EP+optim_purn</t>
+          <t>Wavelet Trans</t>
         </is>
       </c>
       <c r="B212" t="n">
@@ -12473,7 +12473,7 @@
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>Wavelet+50T+50EP+optim_purn</t>
+          <t>Wavelet Trans</t>
         </is>
       </c>
       <c r="B213" t="n">
@@ -12529,7 +12529,7 @@
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>Wavelet+50T+50EP+optim_purn</t>
+          <t>Wavelet Trans</t>
         </is>
       </c>
       <c r="B214" t="n">
@@ -12585,7 +12585,7 @@
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>Wavelet+50T+50EP+optim_purn</t>
+          <t>Wavelet Trans</t>
         </is>
       </c>
       <c r="B215" t="n">
@@ -12641,7 +12641,7 @@
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>Wavelet+50T+50EP+optim_purn</t>
+          <t>Wavelet Trans</t>
         </is>
       </c>
       <c r="B216" t="n">
@@ -12697,7 +12697,7 @@
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>Wavelet+50T+50EP+optim_purn</t>
+          <t>Wavelet Trans</t>
         </is>
       </c>
       <c r="B217" t="n">
@@ -12753,7 +12753,7 @@
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>Wavelet+50T+50EP+optim_purn</t>
+          <t>Wavelet Trans</t>
         </is>
       </c>
       <c r="B218" t="n">
@@ -12809,7 +12809,7 @@
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>Wavelet+50T+50EP+optim_purn</t>
+          <t>Wavelet Trans</t>
         </is>
       </c>
       <c r="B219" t="n">
@@ -12865,7 +12865,7 @@
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>Wavelet+50T+50EP+optim_purn</t>
+          <t>Wavelet Trans</t>
         </is>
       </c>
       <c r="B220" t="n">
@@ -12921,7 +12921,7 @@
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>Wavelet+50T+50EP+optim_purn</t>
+          <t>Wavelet Trans</t>
         </is>
       </c>
       <c r="B221" t="n">
@@ -12977,7 +12977,7 @@
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>Wavelet+50T+50EP+optim_purn</t>
+          <t>Wavelet Trans</t>
         </is>
       </c>
       <c r="B222" t="n">
@@ -13033,7 +13033,7 @@
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>Wavelet+50T+50EP+optim_purn</t>
+          <t>Wavelet Trans</t>
         </is>
       </c>
       <c r="B223" t="n">
@@ -13089,7 +13089,7 @@
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t>Wavelet+50T+50EP+optim_purn</t>
+          <t>Wavelet Trans</t>
         </is>
       </c>
       <c r="B224" t="n">
@@ -13145,7 +13145,7 @@
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t>Wavelet+50T+50EP+optim_purn</t>
+          <t>Wavelet Trans</t>
         </is>
       </c>
       <c r="B225" t="n">
@@ -13201,7 +13201,7 @@
     <row r="226">
       <c r="A226" t="inlineStr">
         <is>
-          <t>Wavelet+50T+50EP+optim_purn</t>
+          <t>Wavelet Trans</t>
         </is>
       </c>
       <c r="B226" t="n">
@@ -13257,7 +13257,7 @@
     <row r="227">
       <c r="A227" t="inlineStr">
         <is>
-          <t>Wavelet+50T+50EP+optim_purn</t>
+          <t>Wavelet Trans</t>
         </is>
       </c>
       <c r="B227" t="n">
@@ -13313,7 +13313,7 @@
     <row r="228">
       <c r="A228" t="inlineStr">
         <is>
-          <t>Wavelet+50T+50EP+optim_purn</t>
+          <t>Wavelet Trans</t>
         </is>
       </c>
       <c r="B228" t="n">
@@ -13369,7 +13369,7 @@
     <row r="229">
       <c r="A229" t="inlineStr">
         <is>
-          <t>Wavelet+50T+50EP+optim_purn</t>
+          <t>Wavelet Trans</t>
         </is>
       </c>
       <c r="B229" t="n">
